--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/134.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/134.xlsx
@@ -426,13 +426,13 @@
         <v>-5.408835665606149</v>
       </c>
       <c r="E2">
-        <v>-20.35977971425423</v>
+        <v>-17.32167240445155</v>
       </c>
       <c r="F2">
-        <v>-1.755679297273906</v>
+        <v>-2.091355306440738</v>
       </c>
       <c r="G2">
-        <v>-11.31676009524999</v>
+        <v>-10.8262612337054</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.139468559225024</v>
       </c>
       <c r="E3">
-        <v>-22.34880245625051</v>
+        <v>-18.54370084503513</v>
       </c>
       <c r="F3">
-        <v>-2.095488031413305</v>
+        <v>-1.624159404731429</v>
       </c>
       <c r="G3">
-        <v>-12.21495152677054</v>
+        <v>-10.70665258100814</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.98317364472459</v>
       </c>
       <c r="E4">
-        <v>-21.9555348759025</v>
+        <v>-19.26095628762169</v>
       </c>
       <c r="F4">
-        <v>-1.799992811486665</v>
+        <v>-1.846648948714542</v>
       </c>
       <c r="G4">
-        <v>-11.98195693110893</v>
+        <v>-10.65692181266432</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.830355967366545</v>
       </c>
       <c r="E5">
-        <v>-22.89080068735196</v>
+        <v>-19.9982592812732</v>
       </c>
       <c r="F5">
-        <v>-1.574553451182183</v>
+        <v>-1.728293470937354</v>
       </c>
       <c r="G5">
-        <v>-12.10639937741664</v>
+        <v>-11.42905735771984</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.672160627650367</v>
       </c>
       <c r="E6">
-        <v>-24.40501585105988</v>
+        <v>-21.23352815956033</v>
       </c>
       <c r="F6">
-        <v>-1.036617458376003</v>
+        <v>-1.259657866681979</v>
       </c>
       <c r="G6">
-        <v>-12.56675719265683</v>
+        <v>-11.99074078128573</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.452103491189332</v>
       </c>
       <c r="E7">
-        <v>-24.48090332838714</v>
+        <v>-21.81750289752182</v>
       </c>
       <c r="F7">
-        <v>-2.259636487584652</v>
+        <v>-1.130221318157542</v>
       </c>
       <c r="G7">
-        <v>-12.77258176935872</v>
+        <v>-12.14400584787933</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.14286034089085</v>
       </c>
       <c r="E8">
-        <v>-24.34932544040525</v>
+        <v>-22.4229372783987</v>
       </c>
       <c r="F8">
-        <v>-0.5159214479568874</v>
+        <v>-1.051069984452647</v>
       </c>
       <c r="G8">
-        <v>-13.05072005511757</v>
+        <v>-12.01294777477774</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.70900454220172</v>
       </c>
       <c r="E9">
-        <v>-25.694982522495</v>
+        <v>-22.78537557108251</v>
       </c>
       <c r="F9">
-        <v>-1.160401227743736</v>
+        <v>-0.5676861269578285</v>
       </c>
       <c r="G9">
-        <v>-12.86841306569242</v>
+        <v>-12.18274668686686</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.11619796704039</v>
       </c>
       <c r="E10">
-        <v>-26.71564666520559</v>
+        <v>-24.11244703249366</v>
       </c>
       <c r="F10">
-        <v>-0.6549612597819788</v>
+        <v>-0.4572465280817928</v>
       </c>
       <c r="G10">
-        <v>-13.40704491989107</v>
+        <v>-11.97103357573971</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.34290831639631</v>
       </c>
       <c r="E11">
-        <v>-28.56055297423032</v>
+        <v>-24.81460139870314</v>
       </c>
       <c r="F11">
-        <v>-0.543853168411884</v>
+        <v>-0.3347707508430803</v>
       </c>
       <c r="G11">
-        <v>-11.53635634967001</v>
+        <v>-11.83303614351494</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.37725788462319</v>
       </c>
       <c r="E12">
-        <v>-28.01181823436</v>
+        <v>-24.90678607726904</v>
       </c>
       <c r="F12">
-        <v>-0.07150647819196668</v>
+        <v>-0.08295285896385024</v>
       </c>
       <c r="G12">
-        <v>-10.94938264325001</v>
+        <v>-11.79625336297075</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.20770680581264</v>
       </c>
       <c r="E13">
-        <v>-30.88233723738886</v>
+        <v>-26.44779776044474</v>
       </c>
       <c r="F13">
-        <v>-0.278639747261983</v>
+        <v>0.3848982813610741</v>
       </c>
       <c r="G13">
-        <v>-12.08848575340471</v>
+        <v>-11.33801677771084</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.8497306580719</v>
       </c>
       <c r="E14">
-        <v>-29.18218903248536</v>
+        <v>-26.74680405656445</v>
       </c>
       <c r="F14">
-        <v>0.02327863350596395</v>
+        <v>0.4689767443778212</v>
       </c>
       <c r="G14">
-        <v>-11.42942938882408</v>
+        <v>-11.09126616879865</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.32457049520608</v>
       </c>
       <c r="E15">
-        <v>-30.58462466659684</v>
+        <v>-29.29084950037685</v>
       </c>
       <c r="F15">
-        <v>0.09572598982000312</v>
+        <v>0.8722417350412737</v>
       </c>
       <c r="G15">
-        <v>-11.43064077431435</v>
+        <v>-10.70933903719239</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.658212845660149</v>
       </c>
       <c r="E16">
-        <v>-31.30938911525869</v>
+        <v>-28.77879592292741</v>
       </c>
       <c r="F16">
-        <v>0.6587408057459375</v>
+        <v>1.021959202688451</v>
       </c>
       <c r="G16">
-        <v>-10.01931140952738</v>
+        <v>-9.299901156861679</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.899853121823186</v>
       </c>
       <c r="E17">
-        <v>-32.92811568874459</v>
+        <v>-29.56117371908729</v>
       </c>
       <c r="F17">
-        <v>1.012703025329569</v>
+        <v>1.442988532304939</v>
       </c>
       <c r="G17">
-        <v>-9.905113524995198</v>
+        <v>-8.891384896967228</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.093427692127525</v>
       </c>
       <c r="E18">
-        <v>-33.42762033817606</v>
+        <v>-30.81671026863958</v>
       </c>
       <c r="F18">
-        <v>1.023049334190535</v>
+        <v>2.057509576602141</v>
       </c>
       <c r="G18">
-        <v>-9.366717943182042</v>
+        <v>-7.926469360559304</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.280309889356147</v>
       </c>
       <c r="E19">
-        <v>-34.00199492816021</v>
+        <v>-31.92092871678307</v>
       </c>
       <c r="F19">
-        <v>1.669489031252408</v>
+        <v>2.100395813779877</v>
       </c>
       <c r="G19">
-        <v>-8.731108675774193</v>
+        <v>-7.758966598338067</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.512643140933133</v>
       </c>
       <c r="E20">
-        <v>-35.39635671945621</v>
+        <v>-33.0066695277424</v>
       </c>
       <c r="F20">
-        <v>1.58739285143056</v>
+        <v>2.492495240220995</v>
       </c>
       <c r="G20">
-        <v>-8.073270223545309</v>
+        <v>-7.084110007492011</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.822440151457843</v>
       </c>
       <c r="E21">
-        <v>-36.62141700430692</v>
+        <v>-33.85425689491341</v>
       </c>
       <c r="F21">
-        <v>1.862197110370073</v>
+        <v>2.898458223515365</v>
       </c>
       <c r="G21">
-        <v>-8.265530676724074</v>
+        <v>-6.866243371363608</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.232579986775855</v>
       </c>
       <c r="E22">
-        <v>-36.32603646167379</v>
+        <v>-34.40218591178671</v>
       </c>
       <c r="F22">
-        <v>2.232116171233832</v>
+        <v>3.283282927425098</v>
       </c>
       <c r="G22">
-        <v>-8.21391756153006</v>
+        <v>-6.443268807923571</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.766228129742665</v>
       </c>
       <c r="E23">
-        <v>-38.23818118544184</v>
+        <v>-35.74520362807953</v>
       </c>
       <c r="F23">
-        <v>2.596463632946361</v>
+        <v>3.416131521281666</v>
       </c>
       <c r="G23">
-        <v>-7.18210691646404</v>
+        <v>-6.065843905364688</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.422888725218107</v>
       </c>
       <c r="E24">
-        <v>-38.00181777573452</v>
+        <v>-36.74428976135197</v>
       </c>
       <c r="F24">
-        <v>2.649394653250444</v>
+        <v>3.857704362487581</v>
       </c>
       <c r="G24">
-        <v>-7.635963977672356</v>
+        <v>-4.908289357812288</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.198567146946752</v>
       </c>
       <c r="E25">
-        <v>-36.67874170361787</v>
+        <v>-37.13006494846999</v>
       </c>
       <c r="F25">
-        <v>3.059542548663757</v>
+        <v>3.81279856558182</v>
       </c>
       <c r="G25">
-        <v>-6.751482871372041</v>
+        <v>-5.710495459068259</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.089662191945901</v>
       </c>
       <c r="E26">
-        <v>-38.51610370427105</v>
+        <v>-36.4026507509829</v>
       </c>
       <c r="F26">
-        <v>2.555381579971922</v>
+        <v>4.290305984721178</v>
       </c>
       <c r="G26">
-        <v>-6.515038176733276</v>
+        <v>-5.823786109855028</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.075353989058833</v>
       </c>
       <c r="E27">
-        <v>-37.48322496705414</v>
+        <v>-36.90027814889554</v>
       </c>
       <c r="F27">
-        <v>2.977510981499328</v>
+        <v>4.399400314935068</v>
       </c>
       <c r="G27">
-        <v>-8.260130351537356</v>
+        <v>-5.645858644481476</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.139276170178498</v>
       </c>
       <c r="E28">
-        <v>-39.72547108013089</v>
+        <v>-37.95757153888546</v>
       </c>
       <c r="F28">
-        <v>3.170200836534132</v>
+        <v>4.089701907520028</v>
       </c>
       <c r="G28">
-        <v>-7.133064079319976</v>
+        <v>-6.196193161309792</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.267490774232069</v>
       </c>
       <c r="E29">
-        <v>-39.65981088569101</v>
+        <v>-37.01951269282004</v>
       </c>
       <c r="F29">
-        <v>3.120588256045664</v>
+        <v>3.831314233769195</v>
       </c>
       <c r="G29">
-        <v>-6.877532230975581</v>
+        <v>-5.70653757026813</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.436350428085783</v>
       </c>
       <c r="E30">
-        <v>-40.1394133464539</v>
+        <v>-37.63217781461346</v>
       </c>
       <c r="F30">
-        <v>2.750970720916524</v>
+        <v>3.914513798971571</v>
       </c>
       <c r="G30">
-        <v>-8.074190511013676</v>
+        <v>-6.241233726995678</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.631201984994568</v>
       </c>
       <c r="E31">
-        <v>-40.00272700854246</v>
+        <v>-37.56639094722817</v>
       </c>
       <c r="F31">
-        <v>3.121040544647592</v>
+        <v>3.916745420754713</v>
       </c>
       <c r="G31">
-        <v>-6.862000911403049</v>
+        <v>-6.135642162008102</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.839565282486228</v>
       </c>
       <c r="E32">
-        <v>-38.66924091224013</v>
+        <v>-37.17829411497956</v>
       </c>
       <c r="F32">
-        <v>2.543986557979012</v>
+        <v>3.834708883385867</v>
       </c>
       <c r="G32">
-        <v>-8.413177420957599</v>
+        <v>-6.283715762982274</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.04238796730298</v>
       </c>
       <c r="E33">
-        <v>-37.65505370259061</v>
+        <v>-37.11940365499916</v>
       </c>
       <c r="F33">
-        <v>2.815957800400951</v>
+        <v>3.323447149317235</v>
       </c>
       <c r="G33">
-        <v>-6.957462787377106</v>
+        <v>-6.653749647603715</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.231170243653101</v>
       </c>
       <c r="E34">
-        <v>-37.07576171039786</v>
+        <v>-37.1145672404114</v>
       </c>
       <c r="F34">
-        <v>2.740672457364921</v>
+        <v>3.471565867877009</v>
       </c>
       <c r="G34">
-        <v>-6.09023609207946</v>
+        <v>-6.823346226987026</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.398356597179015</v>
       </c>
       <c r="E35">
-        <v>-36.85320980495126</v>
+        <v>-36.55189639994062</v>
       </c>
       <c r="F35">
-        <v>1.839062465544689</v>
+        <v>3.354176266491485</v>
       </c>
       <c r="G35">
-        <v>-7.284252298591348</v>
+        <v>-6.179873396870743</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.530972947601051</v>
       </c>
       <c r="E36">
-        <v>-38.40472080635614</v>
+        <v>-36.80265484009978</v>
       </c>
       <c r="F36">
-        <v>1.931465192592168</v>
+        <v>2.831203074082073</v>
       </c>
       <c r="G36">
-        <v>-7.711473238108829</v>
+        <v>-6.482510909872595</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.625655252612491</v>
       </c>
       <c r="E37">
-        <v>-36.19986397823116</v>
+        <v>-36.45414641819945</v>
       </c>
       <c r="F37">
-        <v>1.976700679724243</v>
+        <v>2.772635841969343</v>
       </c>
       <c r="G37">
-        <v>-7.63662971754309</v>
+        <v>-5.621395967662744</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.676256684083921</v>
       </c>
       <c r="E38">
-        <v>-37.13328784045806</v>
+        <v>-35.03002271454972</v>
       </c>
       <c r="F38">
-        <v>2.116548978134467</v>
+        <v>2.702610631941089</v>
       </c>
       <c r="G38">
-        <v>-6.724555651659299</v>
+        <v>-6.296738157002747</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.671757971769209</v>
       </c>
       <c r="E39">
-        <v>-38.56184302059139</v>
+        <v>-34.69017166165598</v>
       </c>
       <c r="F39">
-        <v>1.897374560497357</v>
+        <v>2.393497051912426</v>
       </c>
       <c r="G39">
-        <v>-7.054363183620866</v>
+        <v>-6.102216799008078</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.610248251962437</v>
       </c>
       <c r="E40">
-        <v>-36.58891604908447</v>
+        <v>-34.01802009405706</v>
       </c>
       <c r="F40">
-        <v>2.086875201031383</v>
+        <v>2.370307734838456</v>
       </c>
       <c r="G40">
-        <v>-6.538508770607383</v>
+        <v>-5.264462799399509</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.485616553475492</v>
       </c>
       <c r="E41">
-        <v>-35.06158504401275</v>
+        <v>-33.88712956254943</v>
       </c>
       <c r="F41">
-        <v>1.464627145600867</v>
+        <v>2.17210757984023</v>
       </c>
       <c r="G41">
-        <v>-5.210300292112273</v>
+        <v>-5.454211716281622</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.291297223420864</v>
       </c>
       <c r="E42">
-        <v>-34.02745826679273</v>
+        <v>-33.49205118206378</v>
       </c>
       <c r="F42">
-        <v>1.433970924758063</v>
+        <v>2.213903685515882</v>
       </c>
       <c r="G42">
-        <v>-6.903292447856097</v>
+        <v>-4.69214842385861</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.029546232203836</v>
       </c>
       <c r="E43">
-        <v>-33.53170604379325</v>
+        <v>-32.96897913496958</v>
       </c>
       <c r="F43">
-        <v>1.757080600424427</v>
+        <v>2.038334527962138</v>
       </c>
       <c r="G43">
-        <v>-6.083633519008534</v>
+        <v>-4.39197806449536</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.699227067784899</v>
       </c>
       <c r="E44">
-        <v>-33.5874172205045</v>
+        <v>-32.51466350135791</v>
       </c>
       <c r="F44">
-        <v>2.136761142762775</v>
+        <v>1.778175804704119</v>
       </c>
       <c r="G44">
-        <v>-5.675600246863438</v>
+        <v>-4.198762078796248</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.303487261985167</v>
       </c>
       <c r="E45">
-        <v>-34.00760176344873</v>
+        <v>-32.87255818085236</v>
       </c>
       <c r="F45">
-        <v>1.262097942555611</v>
+        <v>2.083459013862238</v>
       </c>
       <c r="G45">
-        <v>-6.200566158499907</v>
+        <v>-4.375963757173471</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.85373167526362</v>
       </c>
       <c r="E46">
-        <v>-34.29046660375449</v>
+        <v>-32.98082824687931</v>
       </c>
       <c r="F46">
-        <v>1.960134988403059</v>
+        <v>1.870320081121925</v>
       </c>
       <c r="G46">
-        <v>-6.135830135618662</v>
+        <v>-3.796665639851344</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.360365199724057</v>
       </c>
       <c r="E47">
-        <v>-32.92287848926398</v>
+        <v>-30.52866014399477</v>
       </c>
       <c r="F47">
-        <v>1.811214410197375</v>
+        <v>1.626857931234734</v>
       </c>
       <c r="G47">
-        <v>-5.068173967316657</v>
+        <v>-3.313317607741813</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.840936880093911</v>
       </c>
       <c r="E48">
-        <v>-33.2422272144527</v>
+        <v>-30.49505858777125</v>
       </c>
       <c r="F48">
-        <v>0.7304368328256375</v>
+        <v>1.64821489961371</v>
       </c>
       <c r="G48">
-        <v>-6.416780193302135</v>
+        <v>-3.806884094180962</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.317702662113334</v>
       </c>
       <c r="E49">
-        <v>-32.07192909752553</v>
+        <v>-29.8404003462725</v>
       </c>
       <c r="F49">
-        <v>1.086507247449394</v>
+        <v>1.673992036454026</v>
       </c>
       <c r="G49">
-        <v>-5.038479358337335</v>
+        <v>-3.543423414513356</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.808596684230697</v>
       </c>
       <c r="E50">
-        <v>-31.78331828935186</v>
+        <v>-29.52061761050034</v>
       </c>
       <c r="F50">
-        <v>0.9727889703930777</v>
+        <v>1.56121478476729</v>
       </c>
       <c r="G50">
-        <v>-5.813690360521194</v>
+        <v>-3.537084526646133</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.334554647508546</v>
       </c>
       <c r="E51">
-        <v>-31.8651137097887</v>
+        <v>-28.69460617616181</v>
       </c>
       <c r="F51">
-        <v>0.8931513850227388</v>
+        <v>1.391578394552396</v>
       </c>
       <c r="G51">
-        <v>-5.55612213139573</v>
+        <v>-3.790974216642717</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9146881558749963</v>
       </c>
       <c r="E52">
-        <v>-31.47815693404876</v>
+        <v>-28.91936551342756</v>
       </c>
       <c r="F52">
-        <v>0.9300385854694008</v>
+        <v>1.37975262151003</v>
       </c>
       <c r="G52">
-        <v>-4.916369612321784</v>
+        <v>-3.024292517038026</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.5601011807625227</v>
       </c>
       <c r="E53">
-        <v>-29.09208303618754</v>
+        <v>-28.09321079329833</v>
       </c>
       <c r="F53">
-        <v>0.7961893237902511</v>
+        <v>1.378413979787106</v>
       </c>
       <c r="G53">
-        <v>-5.684615147936553</v>
+        <v>-3.204042282136175</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.2826923268267569</v>
       </c>
       <c r="E54">
-        <v>-30.16279545196798</v>
+        <v>-27.24532647151759</v>
       </c>
       <c r="F54">
-        <v>0.6987708321188209</v>
+        <v>1.041490449311657</v>
       </c>
       <c r="G54">
-        <v>-5.422830566296441</v>
+        <v>-2.909819198951481</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.09013603869448521</v>
       </c>
       <c r="E55">
-        <v>-28.54441982483903</v>
+        <v>-26.6782636100708</v>
       </c>
       <c r="F55">
-        <v>0.5247250422188251</v>
+        <v>1.050663789930259</v>
       </c>
       <c r="G55">
-        <v>-5.713346392161754</v>
+        <v>-3.811366742643903</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.0180986074965242</v>
       </c>
       <c r="E56">
-        <v>-27.06079513914414</v>
+        <v>-25.57857216227138</v>
       </c>
       <c r="F56">
-        <v>0.6299674640096967</v>
+        <v>1.157256450587694</v>
       </c>
       <c r="G56">
-        <v>-5.984876883360491</v>
+        <v>-3.959072228630728</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.040926162861067</v>
       </c>
       <c r="E57">
-        <v>-27.89398747586329</v>
+        <v>-26.01617112030061</v>
       </c>
       <c r="F57">
-        <v>1.06589083952852</v>
+        <v>0.7449084113525448</v>
       </c>
       <c r="G57">
-        <v>-5.276091055808328</v>
+        <v>-3.43823390419281</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.01860939071747586</v>
       </c>
       <c r="E58">
-        <v>-27.09411220039191</v>
+        <v>-24.94982580622824</v>
       </c>
       <c r="F58">
-        <v>1.288357189224355</v>
+        <v>0.6478345205206792</v>
       </c>
       <c r="G58">
-        <v>-5.899761388201016</v>
+        <v>-4.12365356765451</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.150203896250196</v>
       </c>
       <c r="E59">
-        <v>-26.47894684538096</v>
+        <v>-24.64334372972384</v>
       </c>
       <c r="F59">
-        <v>0.5849225013802651</v>
+        <v>0.5184203379161181</v>
       </c>
       <c r="G59">
-        <v>-5.847596100525982</v>
+        <v>-4.262996838715999</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.3447744221181538</v>
       </c>
       <c r="E60">
-        <v>-25.18448224608105</v>
+        <v>-24.54206351835657</v>
       </c>
       <c r="F60">
-        <v>0.510897105163893</v>
+        <v>1.091165985722738</v>
       </c>
       <c r="G60">
-        <v>-5.975519974745941</v>
+        <v>-4.77999475786039</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.5897151762667955</v>
       </c>
       <c r="E61">
-        <v>-26.23825578947317</v>
+        <v>-24.12247288463179</v>
       </c>
       <c r="F61">
-        <v>0.82741214793657</v>
+        <v>0.5401177652976455</v>
       </c>
       <c r="G61">
-        <v>-7.58944834129249</v>
+        <v>-4.709786614316172</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.8675231704879512</v>
       </c>
       <c r="E62">
-        <v>-26.96138387287304</v>
+        <v>-23.74159018045442</v>
       </c>
       <c r="F62">
-        <v>0.2000919988987128</v>
+        <v>0.467138597111009</v>
       </c>
       <c r="G62">
-        <v>-6.86024388029323</v>
+        <v>-5.560221000403778</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.162412086521164</v>
       </c>
       <c r="E63">
-        <v>-24.85878741398799</v>
+        <v>-22.01220129121846</v>
       </c>
       <c r="F63">
-        <v>0.8943458908175757</v>
+        <v>0.2466387916294198</v>
       </c>
       <c r="G63">
-        <v>-7.824480623107464</v>
+        <v>-5.808860483027634</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.455904379236042</v>
       </c>
       <c r="E64">
-        <v>-25.63628103362987</v>
+        <v>-22.18787382383606</v>
       </c>
       <c r="F64">
-        <v>0.5591312822941026</v>
+        <v>-0.0677821383489801</v>
       </c>
       <c r="G64">
-        <v>-6.873498630582311</v>
+        <v>-6.372564622907041</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.727687530327696</v>
       </c>
       <c r="E65">
-        <v>-23.45749391299085</v>
+        <v>-22.03263093772529</v>
       </c>
       <c r="F65">
-        <v>0.6405987312572256</v>
+        <v>0.1834219332847756</v>
       </c>
       <c r="G65">
-        <v>-8.517988373312432</v>
+        <v>-5.950511652307667</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.960015677897924</v>
       </c>
       <c r="E66">
-        <v>-24.25389710379466</v>
+        <v>-22.28148720709769</v>
       </c>
       <c r="F66">
-        <v>-0.08860895159016527</v>
+        <v>0.04591294442005765</v>
       </c>
       <c r="G66">
-        <v>-7.736664312668482</v>
+        <v>-6.218924914464615</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.136635472296338</v>
       </c>
       <c r="E67">
-        <v>-25.40414974626255</v>
+        <v>-21.38670274643133</v>
       </c>
       <c r="F67">
-        <v>-0.02852497876290873</v>
+        <v>-0.413347197570433</v>
       </c>
       <c r="G67">
-        <v>-7.261946096804875</v>
+        <v>-6.02893841982471</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.244739953807738</v>
       </c>
       <c r="E68">
-        <v>-25.67288743824691</v>
+        <v>-22.0674597678953</v>
       </c>
       <c r="F68">
-        <v>0.08179616357452663</v>
+        <v>-0.2485840927862086</v>
       </c>
       <c r="G68">
-        <v>-7.624957078476222</v>
+        <v>-6.324871540716583</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.27487447094167</v>
       </c>
       <c r="E69">
-        <v>-23.83095482853075</v>
+        <v>-20.55875176240411</v>
       </c>
       <c r="F69">
-        <v>0.06112508340506777</v>
+        <v>-0.8471217880463942</v>
       </c>
       <c r="G69">
-        <v>-8.163605902514716</v>
+        <v>-6.248332341538916</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.221122462297981</v>
       </c>
       <c r="E70">
-        <v>-25.052327061725</v>
+        <v>-21.39434050205769</v>
       </c>
       <c r="F70">
-        <v>-0.5320770974136863</v>
+        <v>-0.9867919874650161</v>
       </c>
       <c r="G70">
-        <v>-7.966793616141344</v>
+        <v>-5.889524658659261</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.083359806332659</v>
       </c>
       <c r="E71">
-        <v>-23.71733542631742</v>
+        <v>-21.08146248011306</v>
       </c>
       <c r="F71">
-        <v>-0.3118639070534656</v>
+        <v>-1.119459997227774</v>
       </c>
       <c r="G71">
-        <v>-8.209457104396142</v>
+        <v>-6.517087611237299</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.863349919494389</v>
       </c>
       <c r="E72">
-        <v>-24.94181841479396</v>
+        <v>-20.37870174505015</v>
       </c>
       <c r="F72">
-        <v>-0.4901906996911292</v>
+        <v>-1.091332782065716</v>
       </c>
       <c r="G72">
-        <v>-7.79199251741565</v>
+        <v>-6.233975857032384</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.566538106834394</v>
       </c>
       <c r="E73">
-        <v>-25.85516357687099</v>
+        <v>-20.66636146783042</v>
       </c>
       <c r="F73">
-        <v>-0.6416543658234076</v>
+        <v>-0.8645224737096006</v>
       </c>
       <c r="G73">
-        <v>-6.583523228847359</v>
+        <v>-5.905259616309901</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.203792915805203</v>
       </c>
       <c r="E74">
-        <v>-24.53858728047769</v>
+        <v>-21.94506878336393</v>
       </c>
       <c r="F74">
-        <v>-0.9599396297358672</v>
+        <v>-1.276274916782137</v>
       </c>
       <c r="G74">
-        <v>-6.68804699929717</v>
+        <v>-5.578571924134713</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.7829980244548821</v>
       </c>
       <c r="E75">
-        <v>-24.02699886269663</v>
+        <v>-21.47216752907365</v>
       </c>
       <c r="F75">
-        <v>-0.3975966197736033</v>
+        <v>-1.470453348039772</v>
       </c>
       <c r="G75">
-        <v>-6.532584991130148</v>
+        <v>-5.151738680189011</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.3128060347063895</v>
       </c>
       <c r="E76">
-        <v>-24.81279475177684</v>
+        <v>-20.87001833835471</v>
       </c>
       <c r="F76">
-        <v>-1.469015302228512</v>
+        <v>-1.474677193426646</v>
       </c>
       <c r="G76">
-        <v>-5.910530709639358</v>
+        <v>-5.334073082432362</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.1951269381251921</v>
       </c>
       <c r="E77">
-        <v>-23.65377468020224</v>
+        <v>-21.91898661624401</v>
       </c>
       <c r="F77">
-        <v>-0.9252252369867484</v>
+        <v>-1.634069163971119</v>
       </c>
       <c r="G77">
-        <v>-6.691769921084098</v>
+        <v>-4.925867501144253</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.7357037115404471</v>
       </c>
       <c r="E78">
-        <v>-25.45435376475708</v>
+        <v>-22.83620672448709</v>
       </c>
       <c r="F78">
-        <v>-1.458963892162943</v>
+        <v>-1.471204677274111</v>
       </c>
       <c r="G78">
-        <v>-5.509107842798961</v>
+        <v>-4.827878424405998</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.301683991201357</v>
       </c>
       <c r="E79">
-        <v>-24.58419369403563</v>
+        <v>-22.72693573453085</v>
       </c>
       <c r="F79">
-        <v>-1.408998427160882</v>
+        <v>-1.78253331173786</v>
       </c>
       <c r="G79">
-        <v>-4.470193361700523</v>
+        <v>-3.932379975931186</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.88108128372028</v>
       </c>
       <c r="E80">
-        <v>-25.79036102056968</v>
+        <v>-22.11853180755672</v>
       </c>
       <c r="F80">
-        <v>-0.7059563854657193</v>
+        <v>-1.806267694562872</v>
       </c>
       <c r="G80">
-        <v>-5.645819483312609</v>
+        <v>-3.898393302844073</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.466700668269139</v>
       </c>
       <c r="E81">
-        <v>-27.54097697288684</v>
+        <v>-23.19881529883522</v>
       </c>
       <c r="F81">
-        <v>-1.537624832365381</v>
+        <v>-1.971647933062182</v>
       </c>
       <c r="G81">
-        <v>-5.163996126044288</v>
+        <v>-3.506296015683134</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.046863618677268</v>
       </c>
       <c r="E82">
-        <v>-25.39296514816479</v>
+        <v>-24.50849726442931</v>
       </c>
       <c r="F82">
-        <v>-1.391729451914721</v>
+        <v>-1.636736507008133</v>
       </c>
       <c r="G82">
-        <v>-5.606475562324531</v>
+        <v>-3.242454167305225</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.606944643188038</v>
       </c>
       <c r="E83">
-        <v>-26.60549104123716</v>
+        <v>-25.22268348384682</v>
       </c>
       <c r="F83">
-        <v>-1.728438435232844</v>
+        <v>-1.668561554256287</v>
       </c>
       <c r="G83">
-        <v>-3.474601576347018</v>
+        <v>-2.384075285426861</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.136316756603473</v>
       </c>
       <c r="E84">
-        <v>-28.67457939115349</v>
+        <v>-26.31282254559914</v>
       </c>
       <c r="F84">
-        <v>-1.605668587566138</v>
+        <v>-1.72222319460964</v>
       </c>
       <c r="G84">
-        <v>-3.995881116620835</v>
+        <v>-2.579935955396771</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.619336858386756</v>
       </c>
       <c r="E85">
-        <v>-29.61090011827946</v>
+        <v>-27.61291059303287</v>
       </c>
       <c r="F85">
-        <v>-1.089701726649604</v>
+        <v>-1.871864452455759</v>
       </c>
       <c r="G85">
-        <v>-4.290738610741169</v>
+        <v>-1.985508573169142</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.040668086101492</v>
       </c>
       <c r="E86">
-        <v>-29.47490944326494</v>
+        <v>-28.35789702763531</v>
       </c>
       <c r="F86">
-        <v>-1.578986045154563</v>
+        <v>-1.685427114577285</v>
       </c>
       <c r="G86">
-        <v>-2.905615900159789</v>
+        <v>-1.81220212572186</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.387838179245406</v>
       </c>
       <c r="E87">
-        <v>-30.54435720619696</v>
+        <v>-30.20383333306861</v>
       </c>
       <c r="F87">
-        <v>-1.006687715745455</v>
+        <v>-1.470830255208045</v>
       </c>
       <c r="G87">
-        <v>-3.146041980300002</v>
+        <v>-2.046801023934709</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.645137281930881</v>
       </c>
       <c r="E88">
-        <v>-32.12302397984923</v>
+        <v>-31.49903512737868</v>
       </c>
       <c r="F88">
-        <v>-1.961149204599101</v>
+        <v>-1.69441490089766</v>
       </c>
       <c r="G88">
-        <v>-4.186509854430153</v>
+        <v>-1.837589006125846</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.800960478237787</v>
       </c>
       <c r="E89">
-        <v>-32.88568440524448</v>
+        <v>-31.66554775241936</v>
       </c>
       <c r="F89">
-        <v>-1.54371995971518</v>
+        <v>-1.551024503473066</v>
       </c>
       <c r="G89">
-        <v>-3.750904508658311</v>
+        <v>-1.98681655620929</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.844623647801521</v>
       </c>
       <c r="E90">
-        <v>-35.23382079425905</v>
+        <v>-34.01633596686484</v>
       </c>
       <c r="F90">
-        <v>-1.618391482505736</v>
+        <v>-1.489292907881641</v>
       </c>
       <c r="G90">
-        <v>-3.265060604719675</v>
+        <v>-1.995121334753622</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.76632384051007</v>
       </c>
       <c r="E91">
-        <v>-34.70257938048891</v>
+        <v>-35.31240993555312</v>
       </c>
       <c r="F91">
-        <v>-1.435236964644556</v>
+        <v>-1.807800174258051</v>
       </c>
       <c r="G91">
-        <v>-3.606360634371323</v>
+        <v>-2.207615058513514</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.562135453747754</v>
       </c>
       <c r="E92">
-        <v>-37.26479927705876</v>
+        <v>-36.58412739642694</v>
       </c>
       <c r="F92">
-        <v>-1.215118208168255</v>
+        <v>-1.251451230822444</v>
       </c>
       <c r="G92">
-        <v>-2.372303438065531</v>
+        <v>-2.282128319888479</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.228878488274679</v>
       </c>
       <c r="E93">
-        <v>-40.41962220811743</v>
+        <v>-38.86047760429752</v>
       </c>
       <c r="F93">
-        <v>-1.203510295752825</v>
+        <v>-1.233269394698398</v>
       </c>
       <c r="G93">
-        <v>-5.035299471425358</v>
+        <v>-2.610800177952912</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.769324189687585</v>
       </c>
       <c r="E94">
-        <v>-41.44920952535941</v>
+        <v>-40.56466688382008</v>
       </c>
       <c r="F94">
-        <v>-1.048615531838152</v>
+        <v>-1.175995244101437</v>
       </c>
       <c r="G94">
-        <v>-3.580754451421685</v>
+        <v>-2.556715993003409</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.194325326279414</v>
       </c>
       <c r="E95">
-        <v>-40.91679690599567</v>
+        <v>-43.11063526447587</v>
       </c>
       <c r="F95">
-        <v>-2.107336998742949</v>
+        <v>-0.9673642867671592</v>
       </c>
       <c r="G95">
-        <v>-4.728748452281428</v>
+        <v>-3.513112669810531</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.506276196415962</v>
       </c>
       <c r="E96">
-        <v>-45.86211803942099</v>
+        <v>-44.40045865012029</v>
       </c>
       <c r="F96">
-        <v>-2.020162926741941</v>
+        <v>-0.6547723920141406</v>
       </c>
       <c r="G96">
-        <v>-4.568574050127445</v>
+        <v>-3.431756646862258</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.732195187802048</v>
       </c>
       <c r="E97">
-        <v>-46.88982499023565</v>
+        <v>-46.5455081968649</v>
       </c>
       <c r="F97">
-        <v>-1.327938534959936</v>
+        <v>-0.4948784308235716</v>
       </c>
       <c r="G97">
-        <v>-4.627161769496619</v>
+        <v>-4.013072869753316</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.87045751323038</v>
       </c>
       <c r="E98">
-        <v>-48.32782353461881</v>
+        <v>-48.69968857870715</v>
       </c>
       <c r="F98">
-        <v>-0.9084971856546151</v>
+        <v>-0.428576732270902</v>
       </c>
       <c r="G98">
-        <v>-5.192646437187165</v>
+        <v>-4.305899204581764</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.9689870294104752</v>
       </c>
       <c r="E99">
-        <v>-50.50659715732103</v>
+        <v>-51.28850044908705</v>
       </c>
       <c r="F99">
-        <v>-0.6875749127975982</v>
+        <v>-0.1123317372715375</v>
       </c>
       <c r="G99">
-        <v>-6.464744792930069</v>
+        <v>-4.915231327680059</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.001327032689418138</v>
       </c>
       <c r="E100">
-        <v>-52.38590659235498</v>
+        <v>-53.40625509100489</v>
       </c>
       <c r="F100">
-        <v>-1.194541561882715</v>
+        <v>-0.05081634557224343</v>
       </c>
       <c r="G100">
-        <v>-6.142920917928126</v>
+        <v>-5.387123412523785</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.9313248001453942</v>
       </c>
       <c r="E101">
-        <v>-54.12503580045049</v>
+        <v>-55.90195715499628</v>
       </c>
       <c r="F101">
-        <v>-0.5673506381596948</v>
+        <v>0.3732903689456447</v>
       </c>
       <c r="G101">
-        <v>-6.266651936334758</v>
+        <v>-4.994517030167578</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.943352207633122</v>
       </c>
       <c r="E102">
-        <v>-56.87094704240335</v>
+        <v>-58.09379729967782</v>
       </c>
       <c r="F102">
-        <v>-1.14888609247742</v>
+        <v>0.6568695237830134</v>
       </c>
       <c r="G102">
-        <v>-6.67402207935371</v>
+        <v>-5.779520935312703</v>
       </c>
     </row>
   </sheetData>
